--- a/2. zadatak.xlsx
+++ b/2. zadatak.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HOME\Desktop\FM-seminarski\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\FM-git\FM-seminarski\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E828BF44-B027-43B7-A887-A9C3087DBB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F6D1EA-9837-46CC-A7A6-D02A119225EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test case 1" sheetId="1" r:id="rId1"/>
@@ -100,9 +100,6 @@
     <t>User is successfully logged in and redirected to home page</t>
   </si>
   <si>
-    <t>Invalid login using empty email and existing correct password</t>
-  </si>
-  <si>
     <t>Valid login using existing correctly formatted email and matching password</t>
   </si>
   <si>
@@ -440,6 +437,9 @@
   </si>
   <si>
     <t>Cursor is blinking in field "Email"</t>
+  </si>
+  <si>
+    <t>Testing the option for adding new review</t>
   </si>
 </sst>
 </file>
@@ -688,64 +688,14 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -756,29 +706,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -788,6 +732,62 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1073,175 +1073,175 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="2">
         <v>1</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="19"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="15" t="s">
+      <c r="G2" s="23"/>
+      <c r="H2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="19"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="23"/>
     </row>
     <row r="4" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="6" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="21">
+      <c r="E6" s="33"/>
+      <c r="F6" s="39">
         <v>46021</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="15" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="19"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="23"/>
     </row>
     <row r="8" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
     </row>
     <row r="9" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="23"/>
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="19"/>
+      <c r="G9" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
+      <c r="B10" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
       <c r="F10" s="2">
         <v>2</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="19"/>
+      <c r="G10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>3</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="19"/>
+      <c r="B11" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
       <c r="F11" s="2">
         <v>3</v>
       </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="19"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="23"/>
     </row>
     <row r="12" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>4</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
       <c r="F12" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="19"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="23"/>
     </row>
     <row r="14" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1252,100 +1252,100 @@
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="23" t="s">
+      <c r="C16" s="33"/>
+      <c r="D16" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="23" t="s">
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="24" t="s">
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="K16" s="16"/>
+      <c r="K16" s="33"/>
     </row>
     <row r="17" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>1</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="49"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="19"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="27"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2</v>
       </c>
-      <c r="B18" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="57" t="s">
+      <c r="B18" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="58"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="52"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="19"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="16"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="23"/>
     </row>
     <row r="19" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>3</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="19"/>
+      <c r="G19" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="22"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="23"/>
     </row>
     <row r="20" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>4</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="7" t="s">
@@ -1353,52 +1353,59 @@
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="10"/>
-      <c r="G20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" s="19"/>
+      <c r="G20" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="22"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="23"/>
     </row>
     <row r="21" spans="1:11" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>5</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="18"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="22"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:K9"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="G10:K10"/>
     <mergeCell ref="G11:K11"/>
@@ -1413,24 +1420,17 @@
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:G6">
     <cfRule type="notContainsBlanks" dxfId="6" priority="1">
@@ -1455,173 +1455,173 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="2">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="19"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="15" t="s">
+      <c r="G2" s="23"/>
+      <c r="H2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="22" t="s">
+      <c r="I2" s="33"/>
+      <c r="J2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="19"/>
+      <c r="K2" s="23"/>
     </row>
     <row r="4" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="6" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="21">
+      <c r="E6" s="33"/>
+      <c r="F6" s="39">
         <v>46021</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="15" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="19"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="23"/>
     </row>
     <row r="8" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
     </row>
     <row r="9" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1</v>
       </c>
-      <c r="B9" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
+      <c r="B9" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="46"/>
+      <c r="D9" s="47"/>
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="19"/>
+      <c r="G9" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
       <c r="F10" s="2">
         <v>2</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="19"/>
+      <c r="G10" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>3</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="19"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
       <c r="F11" s="2">
         <v>3</v>
       </c>
-      <c r="G11" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="19"/>
+      <c r="G11" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="23"/>
     </row>
     <row r="12" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>4</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
       <c r="F12" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="19"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="23"/>
     </row>
     <row r="14" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1632,176 +1632,142 @@
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="23" t="s">
+      <c r="C16" s="33"/>
+      <c r="D16" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="23" t="s">
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="24" t="s">
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="K16" s="16"/>
+      <c r="K16" s="33"/>
     </row>
     <row r="17" spans="1:11" ht="29.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="19"/>
+      <c r="B17" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="22"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="19"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="23"/>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>3</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="44"/>
+      <c r="D19" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="19"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="22"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="23"/>
     </row>
     <row r="20" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>4</v>
       </c>
-      <c r="B20" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="25" t="s">
+      <c r="B20" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" s="19"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="42"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="22"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="23"/>
     </row>
     <row r="21" spans="1:11" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>5</v>
       </c>
-      <c r="B21" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="30"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" s="26"/>
+      <c r="B21" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="41"/>
+      <c r="D21" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="42"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="42"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="G10:K10"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
@@ -1816,6 +1782,40 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:G6">
     <cfRule type="notContainsBlanks" dxfId="5" priority="1">
@@ -1843,169 +1843,169 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="2">
         <v>3</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="19"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="15" t="s">
+      <c r="G2" s="23"/>
+      <c r="H2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="22" t="s">
+      <c r="I2" s="33"/>
+      <c r="J2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="19"/>
+      <c r="K2" s="23"/>
     </row>
     <row r="4" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="6" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="21">
+      <c r="E6" s="33"/>
+      <c r="F6" s="39">
         <v>46022</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="15" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="19"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="23"/>
     </row>
     <row r="8" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
     </row>
     <row r="9" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1</v>
       </c>
-      <c r="B9" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
+      <c r="B9" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="46"/>
+      <c r="D9" s="47"/>
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="35"/>
+      <c r="G9" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="53"/>
     </row>
     <row r="10" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
       <c r="F10" s="4">
         <v>2</v>
       </c>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
     </row>
     <row r="11" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>3</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="19"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
       <c r="F11" s="2">
         <v>3</v>
       </c>
-      <c r="G11" s="37"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="39"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="50"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>4</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
       <c r="F12" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="19"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="23"/>
     </row>
     <row r="14" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -2016,176 +2016,142 @@
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="23" t="s">
+      <c r="C16" s="33"/>
+      <c r="D16" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="23" t="s">
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="24" t="s">
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="K16" s="16"/>
+      <c r="K16" s="33"/>
     </row>
     <row r="17" spans="1:11" ht="29.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="19"/>
+      <c r="B17" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="22"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2</v>
       </c>
-      <c r="B18" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="19"/>
+      <c r="B18" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="42"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="23"/>
     </row>
     <row r="19" spans="1:11" s="12" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>3</v>
       </c>
-      <c r="B19" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="30"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="26"/>
+      <c r="B19" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="42"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="42"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="41"/>
     </row>
     <row r="20" spans="1:11" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>4</v>
       </c>
-      <c r="B20" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" s="19"/>
+      <c r="B20" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="41"/>
+      <c r="D20" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" s="42"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="22"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="23"/>
     </row>
     <row r="21" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>5</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="23"/>
+      <c r="D21" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="18"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" s="19"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="22"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="G10:K10"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
@@ -2200,6 +2166,40 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:G6">
     <cfRule type="notContainsBlanks" dxfId="4" priority="1">
@@ -2227,169 +2227,169 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="2">
         <v>4</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="19"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="15" t="s">
+      <c r="G2" s="23"/>
+      <c r="H2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="22" t="s">
+      <c r="I2" s="33"/>
+      <c r="J2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="19"/>
+      <c r="K2" s="23"/>
     </row>
     <row r="4" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="6" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="21">
+      <c r="E6" s="33"/>
+      <c r="F6" s="39">
         <v>46022</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="15" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="19"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="23"/>
     </row>
     <row r="8" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
     </row>
     <row r="9" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1</v>
       </c>
-      <c r="B9" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
+      <c r="B9" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="46"/>
+      <c r="D9" s="47"/>
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="19"/>
+      <c r="G9" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
       <c r="F10" s="2">
         <v>2</v>
       </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="19"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>3</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="19"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
       <c r="F11" s="2">
         <v>3</v>
       </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="19"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="23"/>
     </row>
     <row r="12" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>4</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
       <c r="F12" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="19"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="23"/>
     </row>
     <row r="14" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -2400,176 +2400,142 @@
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="23" t="s">
+      <c r="C16" s="33"/>
+      <c r="D16" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="23" t="s">
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="24" t="s">
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="K16" s="16"/>
+      <c r="K16" s="33"/>
     </row>
     <row r="17" spans="1:11" ht="29.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="19"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="22"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="19"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="23"/>
     </row>
     <row r="19" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>3</v>
       </c>
-      <c r="B19" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="19"/>
+      <c r="B19" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="42"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="22"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="23"/>
     </row>
     <row r="20" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>4</v>
       </c>
-      <c r="B20" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" s="19"/>
+      <c r="B20" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="42"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="22"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="23"/>
     </row>
     <row r="21" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>5</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="23"/>
+      <c r="D21" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="18"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" s="19"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="22"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="G10:K10"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
@@ -2584,6 +2550,40 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:G6">
     <cfRule type="notContainsBlanks" dxfId="3" priority="1">
@@ -2612,175 +2612,175 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="2">
         <v>5</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="19"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="15" t="s">
+      <c r="G2" s="23"/>
+      <c r="H2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="22" t="s">
+      <c r="I2" s="33"/>
+      <c r="J2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="19"/>
+      <c r="K2" s="23"/>
     </row>
     <row r="4" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="6" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="21">
+      <c r="E6" s="33"/>
+      <c r="F6" s="39">
         <v>46022</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="15" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="K6" s="19"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="K6" s="23"/>
     </row>
     <row r="8" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
     </row>
     <row r="9" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1</v>
       </c>
-      <c r="B9" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
+      <c r="B9" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="46"/>
+      <c r="D9" s="47"/>
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="19"/>
+      <c r="G9" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
       <c r="F10" s="2">
         <v>2</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="19"/>
+      <c r="G10" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>3</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="19"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
       <c r="F11" s="2">
         <v>3</v>
       </c>
-      <c r="G11" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="19"/>
+      <c r="G11" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="23"/>
     </row>
     <row r="12" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>4</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
       <c r="F12" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="19"/>
+      <c r="G12" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="23"/>
     </row>
     <row r="14" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -2791,337 +2791,331 @@
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="23" t="s">
+      <c r="C16" s="33"/>
+      <c r="D16" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="23" t="s">
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="24" t="s">
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="K16" s="16"/>
+      <c r="K16" s="33"/>
     </row>
     <row r="17" spans="1:11" ht="29.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="19"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="22"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="41"/>
+      <c r="D18" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="19"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="23"/>
     </row>
     <row r="19" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>3</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="23"/>
+      <c r="D19" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="19"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="22"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="23"/>
     </row>
     <row r="20" spans="1:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>4</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" s="19"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="22"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="23"/>
     </row>
     <row r="21" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <v>5</v>
       </c>
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="56"/>
+      <c r="D21" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="44"/>
-      <c r="D21" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="34"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" s="35"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="52"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>6</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="K22" s="40"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="35"/>
     </row>
     <row r="23" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>7</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="57"/>
+      <c r="D23" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="K23" s="40"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>8</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="58"/>
+      <c r="D24" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24" s="40"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" s="35"/>
     </row>
     <row r="25" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>9</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="K25" s="40"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25" s="35"/>
     </row>
     <row r="26" spans="1:11" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>10</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="58"/>
+      <c r="D26" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="K26" s="40"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" s="35"/>
     </row>
     <row r="27" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>11</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="57" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="K27" s="40"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" s="35"/>
     </row>
     <row r="28" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>12</v>
       </c>
-      <c r="B28" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40" t="s">
+      <c r="B28" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="35"/>
+      <c r="D28" s="57" t="s">
         <v>106</v>
       </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40" t="s">
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="K28" s="40"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="K28" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
@@ -3136,34 +3130,40 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:G6">
     <cfRule type="notContainsBlanks" dxfId="2" priority="1">
@@ -3191,173 +3191,173 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="2">
         <v>6</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="19"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="15" t="s">
+      <c r="G2" s="23"/>
+      <c r="H2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="22" t="s">
+      <c r="I2" s="33"/>
+      <c r="J2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="19"/>
+      <c r="K2" s="23"/>
     </row>
     <row r="4" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="6" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="21">
+      <c r="E6" s="33"/>
+      <c r="F6" s="39">
         <v>46022</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="15" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="19"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="23"/>
     </row>
     <row r="8" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
     </row>
     <row r="9" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1</v>
       </c>
-      <c r="B9" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
+      <c r="B9" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="46"/>
+      <c r="D9" s="47"/>
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="19"/>
+      <c r="G9" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="29"/>
+      <c r="B10" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="D10" s="47"/>
       <c r="F10" s="2">
         <v>2</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="19"/>
+      <c r="G10" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>3</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="19"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
       <c r="F11" s="2">
         <v>3</v>
       </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="19"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="23"/>
     </row>
     <row r="12" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>4</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
       <c r="F12" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="19"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="23"/>
     </row>
     <row r="14" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -3368,165 +3368,201 @@
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="23" t="s">
+      <c r="C16" s="33"/>
+      <c r="D16" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="23" t="s">
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="24" t="s">
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="K16" s="16"/>
+      <c r="K16" s="33"/>
     </row>
     <row r="17" spans="1:11" ht="29.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="19"/>
+      <c r="B17" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="22"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2</v>
       </c>
-      <c r="B18" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="19"/>
+      <c r="B18" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="41"/>
+      <c r="D18" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="22"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="23"/>
     </row>
     <row r="19" spans="1:11" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>3</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="19"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="22"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="23"/>
     </row>
     <row r="20" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>4</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" s="19"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="22"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="23"/>
     </row>
     <row r="21" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <v>5</v>
       </c>
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="56"/>
+      <c r="D21" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="C21" s="44"/>
-      <c r="D21" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="34"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" s="35"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="52"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>6</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="K22" s="40"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="G18:I18"/>
@@ -3543,42 +3579,6 @@
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="J20:K20"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="G10:K10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:G6">
     <cfRule type="notContainsBlanks" dxfId="1" priority="1">
@@ -3607,169 +3607,169 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="2">
         <v>7</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="19"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D2" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="15" t="s">
+      <c r="G2" s="23"/>
+      <c r="H2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="22" t="s">
+      <c r="I2" s="33"/>
+      <c r="J2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="19"/>
+      <c r="K2" s="23"/>
     </row>
     <row r="4" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="6" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="21">
+      <c r="E6" s="33"/>
+      <c r="F6" s="39">
         <v>46022</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="15" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="19"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="23"/>
     </row>
     <row r="8" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
     </row>
     <row r="9" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1</v>
       </c>
-      <c r="B9" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
+      <c r="B9" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="46"/>
+      <c r="D9" s="47"/>
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="19"/>
+      <c r="G9" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
       <c r="F10" s="2">
         <v>2</v>
       </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="19"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>3</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="19"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
       <c r="F11" s="2">
         <v>3</v>
       </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="19"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="23"/>
     </row>
     <row r="12" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>4</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
       <c r="F12" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="19"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="23"/>
     </row>
     <row r="14" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -3780,165 +3780,201 @@
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="23" t="s">
+      <c r="C16" s="33"/>
+      <c r="D16" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="23" t="s">
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="24" t="s">
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="K16" s="16"/>
+      <c r="K16" s="33"/>
     </row>
     <row r="17" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="19"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="22"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="41"/>
+      <c r="D18" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="19"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="23"/>
     </row>
     <row r="19" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>3</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="19"/>
+      <c r="B19" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="23"/>
+      <c r="D19" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="42"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="22"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="23"/>
     </row>
     <row r="20" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>4</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" s="19"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="22"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="23"/>
     </row>
     <row r="21" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <v>5</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="C21" s="53"/>
+      <c r="D21" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="34"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" s="35"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="52"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>6</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="35"/>
+      <c r="D22" s="57" t="s">
         <v>133</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="K22" s="40"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="G18:I18"/>
@@ -3955,42 +3991,6 @@
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="J20:K20"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="G10:K10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:G6">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
